--- a/ig/DM-JANVIER-2025/ASS-A29-Departement-AE.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-A29-Departement-AE.xlsx
@@ -42,7 +42,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASS_A29_Département_AE</t>
+    <t>ASS_A29_Departement_AE</t>
   </si>
   <si>
     <t>Title</t>
